--- a/WWC_3.0与5.0评级对照.xlsx
+++ b/WWC_3.0与5.0评级对照.xlsx
@@ -111,7 +111,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">15</t>
     </r>
     <r>
       <rPr>
@@ -294,6 +294,189 @@
     <t xml:space="preserve">10 Haley et al. 2010</t>
   </si>
   <si>
+    <t xml:space="preserve">11 Hochman et al. 2015</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仅提取</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Brody</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Taylor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Kevin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（均</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岁）的数据，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Matthew</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岁）不提取；去掉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Matthew</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">为有保留（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Brody</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">17 Kern &amp; Aldridge 2006</t>
   </si>
   <si>
@@ -404,6 +587,25 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">007-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不同教学形式与环境下同伴支持安排对重度障碍学生的影响</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">008-A </t>
     </r>
     <r>
@@ -912,6 +1114,25 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">007-B I-SOCIALISE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：探究在学校环境中参加乐高疗法（“积木游戏疗法”）俱乐部的孤独症儿童社会能力与社会孤立状况的整群随机对照试验结果</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">009-B “</t>
     </r>
     <r>
@@ -972,7 +1193,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">15</t>
     </r>
     <r>
       <rPr>
@@ -1083,19 +1304,67 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">岁（高中生）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">11 Hochman et al. 2015</t>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岁（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Anton 18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岁）；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">George 14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岁但仅有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A-B-A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">设计，单独不达标</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">12 Hughes et al. 2011</t>
@@ -1143,6 +1412,50 @@
     <t xml:space="preserve">13 Hughes et al. 2013</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">被试年龄超过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岁（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16–17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岁）</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">14 Jung et al. 2008</t>
   </si>
   <si>
@@ -1380,6 +1693,858 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岁及以下被试仅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P1 14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岁、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P3 15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">岁），多基线设计不成立</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">28 Strain et al. 2011</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rosalie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">首个基线点出现在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Josh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">进入干预的同一次会话</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Josh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">干预前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rosalie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无基线数据，违反</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同时性第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">006-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">提升孤独症谱系障碍学前学生的数感理解</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不符合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0343</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">融合情境定义：干预与测量在治疗室、走廊单独进行</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">012-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">运用结构分析指导重度障碍高中生的同伴支持安排</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次会话中没有三层同时有探测点的会话</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(John 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tyler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Richard 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">014-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全班功能相关干预小组（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CW-FIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）对台湾融合班一名孤独症谱系障碍小学生行为的影响</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IOA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未覆盖每一阶段</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">015-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">运用结构分析探讨孤独症高中生同伴支持安排的效果与个别化</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：首</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次会话内无三层垂直重叠的探测点</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">018-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">多重表征促进孤独症学生早期代数思维的效果</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不符合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0343</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">融合情境定义：研究者个别化教学，无普通同学共享活动</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">023-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在台湾小学融合课堂中实施同伴介入干预向两名孤独症谱系学生和一名注意缺陷多动障碍学生教授行为期望</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：首</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次会话内无三层垂直重叠的探测点；同上</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">026-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">运用三级视频示范模型向一名孤独症幼儿教授身体活动：一项试点研究</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：按</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">其他设计</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条款也不满足：无</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个时间点上对同一干预的效果展示</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">031-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">运用综合分析及据此制定的干预促进重新融入学校</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：同左；治疗延伸期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IOA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6%(&lt;20%)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">032-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">面向发展障碍学生核心学业内容教学的普通教育教师培训</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不符合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0343</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">融合情境定义：基线期在心理咨询室单独测量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">033-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">融合高中课堂中由教学辅助人员实施的低强度同伴培训的探索</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
@@ -1392,7 +2557,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">15</t>
     </r>
     <r>
       <rPr>
@@ -1409,7 +2574,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">14–16</t>
+      <t xml:space="preserve">Max 17</t>
     </r>
     <r>
       <rPr>
@@ -1421,7 +2586,23 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">28 Strain et al. 2011</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">034-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">运用同伴介入与教育工作者引导促进融合托育环境中孤独症谱系障碍幼儿的轮流行为</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1439,41 +2620,162 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">不达标：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rosalie</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">首个基线点出现在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Josh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">进入干预的同一次会话</t>
+      <t xml:space="preserve">不达标：同左</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保留同一条探测要求</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">038-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">共同视频示范对孤独症谱系障碍儿童非脚本化游戏行为的影响</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">041-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社会故事对促进融合情境中伴有孤独症谱系障碍的聋及重听学生社会互动与参与的效果</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：违反同时性要求</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">045-A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">视频示范在教授孤独症谱系障碍儿童身体活动型合作游戏中的有效性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：首</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次会话无垂直重叠；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Efe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">进入干预时其他层尚无基线数据</t>
     </r>
     <r>
       <rPr>
@@ -1490,7 +2792,357 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">第</t>
+      <t xml:space="preserve">违反同时性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">户秀美</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低年级随班就读孤独症儿童发散性思维的干预研究（中文）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不符合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0343</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">融合情境定义：研究者一对一教学，未报告干预情境，无普通同学参与</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">15 Kasari et al. 2016</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下主要结局不达标，仅出度指标有保留；作者决定排除</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">20 Kretzmann et al. 2015</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无法确认儿童是否在学校随机分组前入组</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">需证明基线等同</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；作者决定排除</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">002-B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">孤独症谱系障碍青少年与校内社交技能小组：比较干预环境和同伴构成的随机试验</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">保守流失边界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：同左</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">003-B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加速实现公平：句法引导对孤独症儿童融合教育及可持续发展目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的因果影响</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：同左</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">005-B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">普通教育课堂中孤独症学生的学业与社会参与结果：实施融合实践以提升生活质量所面临的挑战</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不达标：同左；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">还明确要求：学校随机化后才确定的学生须证明基线等同</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">006-B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基于幼儿园的普适性情绪教育项目对</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">至</t>
     </r>
     <r>
       <rPr>
@@ -1507,7 +3159,53 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">次</t>
+      <t xml:space="preserve">岁孤独症谱系儿童的有效性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">008-B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小学柔道与空手道作为促进孤独症儿童社会融合的手段</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两种干预比较、无未干预对照，教练人数未报告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">可能构成混淆</t>
     </r>
     <r>
       <rPr>
@@ -1524,1548 +3222,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Josh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">干预前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Rosalie</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">无基线数据，违反</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">同时性第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">条</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">006-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">提升孤独症谱系障碍学前学生的数感理解</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不符合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0343</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">融合情境定义：干预与测量在治疗室、走廊单独进行</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">007-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不同教学形式与环境下同伴支持安排对重度障碍学生的影响</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">被试年龄超过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">岁（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Adrian 14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">岁）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">012-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">运用结构分析指导重度障碍高中生的同伴支持安排</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">次会话中没有三层同时有探测点的会话</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(John 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Tyler</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Richard 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">014-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">全班功能相关干预小组（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CW-FIT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）对台湾融合班一名孤独症谱系障碍小学生行为的影响</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IOA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未覆盖每一阶段</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">015-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">运用结构分析探讨孤独症高中生同伴支持安排的效果与个别化</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：首</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">次会话内无三层垂直重叠的探测点</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">018-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">多重表征促进孤独症学生早期代数思维的效果</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不符合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0343</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">融合情境定义：研究者个别化教学，无普通同学共享活动</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">023-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">在台湾小学融合课堂中实施同伴介入干预向两名孤独症谱系学生和一名注意缺陷多动障碍学生教授行为期望</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：首</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">次会话内无三层垂直重叠的探测点；同上</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">026-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">运用三级视频示范模型向一名孤独症幼儿教授身体活动：一项试点研究</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：按</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">其他设计</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">条款也不满足：无</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个时间点上对同一干预的效果展示</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">031-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">运用综合分析及据此制定的干预促进重新融入学校</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：同左；治疗延伸期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IOA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6%(&lt;20%)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">032-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">面向发展障碍学生核心学业内容教学的普通教育教师培训</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不符合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0343</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">融合情境定义：基线期在心理咨询室单独测量</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">033-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">融合高中课堂中由教学辅助人员实施的低强度同伴培训的探索</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">被试年龄超过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">岁（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Max 17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">岁）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">034-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">运用同伴介入与教育工作者引导促进融合托育环境中孤独症谱系障碍幼儿的轮流行为</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：同左</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">保留同一条探测要求</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">038-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">共同视频示范对孤独症谱系障碍儿童非脚本化游戏行为的影响</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">041-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社会故事对促进融合情境中伴有孤独症谱系障碍的聋及重听学生社会互动与参与的效果</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：违反同时性要求</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">045-A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">视频示范在教授孤独症谱系障碍儿童身体活动型合作游戏中的有效性</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：首</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">次会话无垂直重叠；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Efe</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">进入干预时其他层尚无基线数据</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">违反同时性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">户秀美</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低年级随班就读孤独症儿童发散性思维的干预研究（中文）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不符合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0343</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">融合情境定义：研究者一对一教学，未报告干预情境，无普通同学参与</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">15 Kasari et al. 2016</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下主要结局不达标，仅出度指标有保留；作者决定排除</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">20 Kretzmann et al. 2015</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">无法确认儿童是否在学校随机分组前入组</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">需证明基线等同</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">；作者决定排除</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">002-B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">孤独症谱系障碍青少年与校内社交技能小组：比较干预环境和同伴构成的随机试验</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">保守流失边界</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：同左</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">003-B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加速实现公平：句法引导对孤独症儿童融合教育及可持续发展目标</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的因果影响</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：同左</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">005-B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">普通教育课堂中孤独症学生的学业与社会参与结果：实施融合实践以提升生活质量所面临的挑战</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不达标：同左；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">还明确要求：学校随机化后才确定的学生须证明基线等同</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">006-B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">基于幼儿园的普适性情绪教育项目对</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">岁孤独症谱系儿童的有效性</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">007-B I-SOCIALISE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：探究在学校环境中参加乐高疗法（“积木游戏疗法”）俱乐部的孤独症儿童社会能力与社会孤立状况的整群随机对照试验结果</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">被试年龄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7–15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">岁，无法单独提取</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">岁及以下被试的数据</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">008-B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小学柔道与空手道作为促进孤独症儿童社会融合的手段</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">两种干预比较、无未干预对照，教练人数未报告</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">可能构成混淆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；作者决定排除</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">融合情境筛选：E列为参考方案（"并且"版，未采用）；G列为最终采用的0343定义</t>
   </si>
   <si>
     <t xml:space="preserve">定义：干预在教室（含资源教室）、课间和操场、午餐等日常自然情境中进行，并且有普通同伴作为共同参与者的小组活动。两个条件同时满足才纳入。</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">最终采用：参照</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Watkins</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">等（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2019</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），融合情境指孤独症学生与普通同班同学共享情境和活动；在特教班或抽离场所由成人单独实施的干预不予纳入。</t>
-    </r>
+    <t xml:space="preserve">最终采用：参照Watkins等（2019），融合情境指孤独症学生与普通同班同学共享情境和活动；在特教班或抽离场所由成人单独实施的干预不予纳入。</t>
   </si>
   <si>
     <t xml:space="preserve">干预与测量情境</t>
@@ -14123,7 +14290,6 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
       <charset val="1"/>
@@ -14131,6 +14297,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
       <charset val="1"/>
@@ -14306,11 +14473,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14318,7 +14485,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14330,11 +14497,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14354,11 +14521,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14766,7 +14933,7 @@
       </c>
       <c r="C4" s="5" t="n">
         <f aca="false">COUNTIFS($A$12:$A$93,"母本",$B$12:$B$93,"单一被试",$E$12:$E$93,"纳入")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5" t="n">
         <f aca="false">COUNTIFS($A$12:$A$93,"母本",$B$12:$B$93,"组间设计",$E$12:$E$93,"纳入")</f>
@@ -14774,7 +14941,7 @@
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">C4+D4</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14783,15 +14950,15 @@
       </c>
       <c r="C5" s="5" t="n">
         <f aca="false">COUNTIFS($A$12:$A$93,"新检索",$B$12:$B$93,"单一被试",$E$12:$E$93,"纳入")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="5" t="n">
         <f aca="false">COUNTIFS($A$12:$A$93,"新检索",$B$12:$B$93,"组间设计",$E$12:$E$93,"纳入")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">C5+D5</f>
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14817,15 +14984,15 @@
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C4:C6)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D7" s="7" t="n">
         <f aca="false">SUM(D4:D6)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="7" t="n">
         <f aca="false">SUM(E4:E6)</f>
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14834,15 +15001,15 @@
       </c>
       <c r="C8" s="5" t="n">
         <f aca="false">COUNTIFS($B$12:$B$93,"单一被试",$E$12:$E$93,"排除")</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D8" s="5" t="n">
         <f aca="false">COUNTIFS($B$12:$B$93,"组间设计",$E$12:$E$93,"排除")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="5" t="n">
         <f aca="false">C8+D8</f>
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15022,7 +15189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
         <v>16</v>
       </c>
@@ -15033,13 +15200,13 @@
         <v>28</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>20</v>
+      <c r="F19" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15050,10 +15217,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>19</v>
@@ -15070,10 +15237,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>19</v>
@@ -15090,10 +15257,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>19</v>
@@ -15110,7 +15277,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>18</v>
@@ -15130,7 +15297,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>18</v>
@@ -15150,10 +15317,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>19</v>
@@ -15170,7 +15337,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>26</v>
@@ -15182,9 +15349,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>1</v>
@@ -15193,7 +15360,7 @@
         <v>37</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>19</v>
@@ -15202,18 +15369,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>19</v>
@@ -15222,18 +15389,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>19</v>
@@ -15244,13 +15411,13 @@
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>18</v>
@@ -15264,16 +15431,16 @@
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>19</v>
@@ -15282,15 +15449,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>18</v>
@@ -15304,16 +15471,16 @@
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>19</v>
@@ -15322,15 +15489,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B34" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>18</v>
@@ -15344,13 +15511,13 @@
     </row>
     <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>18</v>
@@ -15364,13 +15531,13 @@
     </row>
     <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>18</v>
@@ -15384,13 +15551,13 @@
     </row>
     <row r="37" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>18</v>
@@ -15404,13 +15571,13 @@
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>18</v>
@@ -15422,15 +15589,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>18</v>
@@ -15444,13 +15611,13 @@
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>18</v>
@@ -15462,15 +15629,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>18</v>
@@ -15484,13 +15651,13 @@
     </row>
     <row r="42" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>18</v>
@@ -15504,13 +15671,13 @@
     </row>
     <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>18</v>
@@ -15524,13 +15691,13 @@
     </row>
     <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>18</v>
@@ -15544,16 +15711,16 @@
     </row>
     <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>19</v>
@@ -15564,16 +15731,16 @@
     </row>
     <row r="46" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>19</v>
@@ -15584,16 +15751,16 @@
     </row>
     <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>19</v>
@@ -15604,16 +15771,16 @@
     </row>
     <row r="48" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>19</v>
@@ -15624,13 +15791,13 @@
     </row>
     <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B49" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>18</v>
@@ -15644,13 +15811,13 @@
     </row>
     <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>18</v>
@@ -15662,15 +15829,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B51" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>18</v>
@@ -15684,13 +15851,13 @@
     </row>
     <row r="52" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B52" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>18</v>
@@ -15702,18 +15869,18 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>19</v>
@@ -15724,16 +15891,16 @@
     </row>
     <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B54" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>19</v>
@@ -15744,16 +15911,16 @@
     </row>
     <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="11" t="s">
         <v>66</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>19</v>
@@ -15762,12 +15929,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" s="11" t="s">
         <v>67</v>
@@ -15784,16 +15951,16 @@
     </row>
     <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>68</v>
+        <v>1</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>69</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>19</v>
@@ -15802,15 +15969,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>26</v>
@@ -15824,13 +15991,13 @@
     </row>
     <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>70</v>
+      <c r="C59" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>26</v>
@@ -15842,64 +16009,64 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F60" s="10" t="s">
-        <v>73</v>
+        <v>18</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D61" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>76</v>
-      </c>
       <c r="D62" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>77</v>
+        <v>26</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15910,19 +16077,19 @@
         <v>1</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
         <v>16</v>
       </c>
@@ -15930,16 +16097,16 @@
         <v>1</v>
       </c>
       <c r="C64" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F64" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15950,19 +16117,19 @@
         <v>1</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>18</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
         <v>16</v>
       </c>
@@ -15970,13 +16137,13 @@
         <v>1</v>
       </c>
       <c r="C66" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D66" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D66" s="10" t="s">
-        <v>80</v>
-      </c>
       <c r="E66" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F66" s="11" t="s">
         <v>84</v>
@@ -15993,16 +16160,16 @@
         <v>85</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F67" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F67" s="10" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
         <v>16</v>
       </c>
@@ -16013,16 +16180,16 @@
         <v>87</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F68" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F68" s="11" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
         <v>16</v>
       </c>
@@ -16033,10 +16200,10 @@
         <v>89</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F69" s="11" t="s">
         <v>90</v>
@@ -16044,7 +16211,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>1</v>
@@ -16056,15 +16223,15 @@
         <v>18</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F70" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F70" s="11" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>1</v>
@@ -16073,18 +16240,18 @@
         <v>93</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F71" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F71" s="11" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>1</v>
@@ -16093,18 +16260,18 @@
         <v>95</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F72" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F72" s="10" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>1</v>
@@ -16113,10 +16280,10 @@
         <v>97</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F73" s="11" t="s">
         <v>98</v>
@@ -16124,7 +16291,7 @@
     </row>
     <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>1</v>
@@ -16133,18 +16300,18 @@
         <v>99</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F74" s="11" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>1</v>
@@ -16153,18 +16320,18 @@
         <v>101</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F75" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F75" s="11" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>1</v>
@@ -16173,18 +16340,18 @@
         <v>103</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F76" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F76" s="10" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>1</v>
@@ -16193,18 +16360,18 @@
         <v>105</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F77" s="11" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>1</v>
@@ -16213,18 +16380,18 @@
         <v>107</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F78" s="11" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>1</v>
@@ -16233,18 +16400,18 @@
         <v>109</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F79" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F79" s="11" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>1</v>
@@ -16256,7 +16423,7 @@
         <v>18</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F80" s="10" t="s">
         <v>112</v>
@@ -16264,7 +16431,7 @@
     </row>
     <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B81" s="10" t="s">
         <v>1</v>
@@ -16273,18 +16440,18 @@
         <v>113</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F81" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F81" s="10" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>1</v>
@@ -16293,38 +16460,38 @@
         <v>115</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C83" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F83" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F83" s="11" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>1</v>
@@ -16333,10 +16500,10 @@
         <v>118</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F84" s="11" t="s">
         <v>119</v>
@@ -16344,41 +16511,41 @@
     </row>
     <row r="85" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="10" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C85" s="11" t="s">
         <v>120</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F85" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F85" s="11" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="10" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C86" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C86" s="10" t="s">
         <v>122</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>18</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F86" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F86" s="10" t="s">
         <v>123</v>
       </c>
     </row>
@@ -16393,18 +16560,18 @@
         <v>124</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F87" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F87" s="11" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="10" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>2</v>
@@ -16413,18 +16580,18 @@
         <v>126</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F88" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F88" s="10" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>2</v>
@@ -16433,10 +16600,10 @@
         <v>128</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F89" s="11" t="s">
         <v>129</v>
@@ -16444,7 +16611,7 @@
     </row>
     <row r="90" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B90" s="10" t="s">
         <v>2</v>
@@ -16453,10 +16620,10 @@
         <v>130</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F90" s="11" t="s">
         <v>131</v>
@@ -16464,7 +16631,7 @@
     </row>
     <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>2</v>
@@ -16473,38 +16640,38 @@
         <v>132</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F92" s="10" t="s">
-        <v>134</v>
+        <v>76</v>
+      </c>
+      <c r="F92" s="11" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>2</v>
@@ -16516,7 +16683,7 @@
         <v>26</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>136</v>
@@ -16567,7 +16734,7 @@
       <c r="E2" s="16"/>
       <c r="F2" s="16"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
         <v>139</v>
       </c>
@@ -16580,7 +16747,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>3</v>
@@ -16605,7 +16772,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">COUNTIFS($B$11:$B$66,A6,$E$11:$E$66,"纳入")</f>
@@ -16622,7 +16789,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">COUNTIFS($B$11:$B$66,A7,$E$11:$E$66,"纳入")</f>
@@ -16679,7 +16846,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>16</v>
@@ -16697,12 +16864,12 @@
         <v>20</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>16</v>
@@ -16725,7 +16892,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>16</v>
@@ -16748,7 +16915,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>16</v>
@@ -16771,7 +16938,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>16</v>
@@ -16794,7 +16961,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>16</v>
@@ -16817,7 +16984,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>16</v>
@@ -16840,7 +17007,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>16</v>
@@ -16863,7 +17030,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>16</v>
@@ -16886,7 +17053,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>16</v>
@@ -16912,7 +17079,7 @@
         <v>161</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>162</v>
@@ -16935,7 +17102,7 @@
         <v>164</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>165</v>
@@ -16958,7 +17125,7 @@
         <v>168</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>169</v>
@@ -16981,7 +17148,7 @@
         <v>171</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>172</v>
@@ -17004,7 +17171,7 @@
         <v>174</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>175</v>
@@ -17027,7 +17194,7 @@
         <v>177</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>178</v>
@@ -17050,7 +17217,7 @@
         <v>179</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>149</v>
@@ -17073,7 +17240,7 @@
         <v>181</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C28" s="19" t="s">
         <v>182</v>
@@ -17096,7 +17263,7 @@
         <v>184</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>185</v>
@@ -17119,7 +17286,7 @@
         <v>187</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C30" s="19" t="s">
         <v>188</v>
@@ -17142,7 +17309,7 @@
         <v>190</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>191</v>
@@ -17165,7 +17332,7 @@
         <v>193</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C32" s="19" t="s">
         <v>194</v>
@@ -17188,7 +17355,7 @@
         <v>196</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>149</v>
@@ -17211,7 +17378,7 @@
         <v>198</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>149</v>
@@ -17234,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>201</v>
@@ -17257,7 +17424,7 @@
         <v>203</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C36" s="19" t="s">
         <v>204</v>
@@ -17280,7 +17447,7 @@
         <v>206</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C37" s="19" t="s">
         <v>207</v>
@@ -17303,7 +17470,7 @@
         <v>209</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C38" s="19" t="s">
         <v>149</v>
@@ -17326,7 +17493,7 @@
         <v>211</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C39" s="19" t="s">
         <v>212</v>
@@ -17349,7 +17516,7 @@
         <v>214</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C40" s="19" t="s">
         <v>215</v>
@@ -17381,7 +17548,7 @@
         <v>218</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F41" s="19" t="s">
         <v>219</v>
@@ -17404,7 +17571,7 @@
         <v>221</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F42" s="19" t="s">
         <v>219</v>
@@ -17427,7 +17594,7 @@
         <v>223</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F43" s="19" t="s">
         <v>219</v>
@@ -17450,7 +17617,7 @@
         <v>225</v>
       </c>
       <c r="E44" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F44" s="19" t="s">
         <v>219</v>
@@ -17473,7 +17640,7 @@
         <v>226</v>
       </c>
       <c r="E45" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F45" s="19" t="s">
         <v>219</v>
@@ -17484,7 +17651,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>16</v>
@@ -17496,7 +17663,7 @@
         <v>227</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F46" s="19" t="s">
         <v>219</v>
@@ -17519,7 +17686,7 @@
         <v>228</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F47" s="19" t="s">
         <v>219</v>
@@ -17542,7 +17709,7 @@
         <v>229</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F48" s="19" t="s">
         <v>219</v>
@@ -17553,7 +17720,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>16</v>
@@ -17565,7 +17732,7 @@
         <v>231</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F49" s="19" t="s">
         <v>219</v>
@@ -17576,7 +17743,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>16</v>
@@ -17588,7 +17755,7 @@
         <v>227</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F50" s="19" t="s">
         <v>219</v>
@@ -17599,7 +17766,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>16</v>
@@ -17611,7 +17778,7 @@
         <v>233</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F51" s="19" t="s">
         <v>219</v>
@@ -17625,7 +17792,7 @@
         <v>234</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C52" s="19" t="s">
         <v>235</v>
@@ -17634,7 +17801,7 @@
         <v>236</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F52" s="19" t="s">
         <v>237</v>
@@ -17648,7 +17815,7 @@
         <v>238</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C53" s="19" t="s">
         <v>239</v>
@@ -17657,13 +17824,13 @@
         <v>240</v>
       </c>
       <c r="E53" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F53" s="19" t="s">
         <v>241</v>
       </c>
       <c r="G53" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17671,7 +17838,7 @@
         <v>242</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C54" s="19" t="s">
         <v>243</v>
@@ -17680,7 +17847,7 @@
         <v>244</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F54" s="19" t="s">
         <v>219</v>
@@ -17694,7 +17861,7 @@
         <v>245</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C55" s="19" t="s">
         <v>149</v>
@@ -17703,7 +17870,7 @@
         <v>246</v>
       </c>
       <c r="E55" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F55" s="19" t="s">
         <v>219</v>
@@ -17717,7 +17884,7 @@
         <v>247</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C56" s="19" t="s">
         <v>248</v>
@@ -17726,7 +17893,7 @@
         <v>249</v>
       </c>
       <c r="E56" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F56" s="19" t="s">
         <v>219</v>
@@ -17740,7 +17907,7 @@
         <v>250</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>251</v>
@@ -17749,13 +17916,13 @@
         <v>240</v>
       </c>
       <c r="E57" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F57" s="19" t="s">
         <v>252</v>
       </c>
       <c r="G57" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17763,7 +17930,7 @@
         <v>253</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C58" s="19" t="s">
         <v>243</v>
@@ -17772,7 +17939,7 @@
         <v>254</v>
       </c>
       <c r="E58" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F58" s="19" t="s">
         <v>219</v>
@@ -17786,7 +17953,7 @@
         <v>255</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C59" s="19" t="s">
         <v>256</v>
@@ -17795,7 +17962,7 @@
         <v>257</v>
       </c>
       <c r="E59" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F59" s="19" t="s">
         <v>219</v>
@@ -17809,7 +17976,7 @@
         <v>258</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C60" s="19" t="s">
         <v>259</v>
@@ -17818,7 +17985,7 @@
         <v>260</v>
       </c>
       <c r="E60" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F60" s="19" t="s">
         <v>219</v>
@@ -17832,7 +17999,7 @@
         <v>261</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C61" s="19" t="s">
         <v>262</v>
@@ -17841,13 +18008,13 @@
         <v>263</v>
       </c>
       <c r="E61" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F61" s="19" t="s">
         <v>264</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17855,7 +18022,7 @@
         <v>265</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C62" s="19" t="s">
         <v>266</v>
@@ -17864,7 +18031,7 @@
         <v>267</v>
       </c>
       <c r="E62" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F62" s="19" t="s">
         <v>219</v>
@@ -17878,7 +18045,7 @@
         <v>268</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C63" s="19" t="s">
         <v>259</v>
@@ -17887,7 +18054,7 @@
         <v>269</v>
       </c>
       <c r="E63" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F63" s="19" t="s">
         <v>219</v>
@@ -17901,7 +18068,7 @@
         <v>270</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C64" s="19" t="s">
         <v>149</v>
@@ -17910,7 +18077,7 @@
         <v>271</v>
       </c>
       <c r="E64" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F64" s="19" t="s">
         <v>219</v>
@@ -17924,7 +18091,7 @@
         <v>272</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C65" s="19" t="s">
         <v>259</v>
@@ -17933,7 +18100,7 @@
         <v>260</v>
       </c>
       <c r="E65" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F65" s="19" t="s">
         <v>219</v>
@@ -17947,7 +18114,7 @@
         <v>273</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C66" s="19" t="s">
         <v>274</v>
@@ -17956,13 +18123,13 @@
         <v>240</v>
       </c>
       <c r="E66" s="25" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F66" s="19" t="s">
         <v>219</v>
       </c>
       <c r="G66" s="23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17998,7 +18165,7 @@
     </row>
     <row r="71" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B71" s="19" t="s">
         <v>16</v>
@@ -18024,7 +18191,7 @@
         <v>280</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C72" s="19" t="s">
         <v>281</v>
@@ -18047,7 +18214,7 @@
         <v>284</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C73" s="19" t="s">
         <v>285</v>
@@ -18070,7 +18237,7 @@
         <v>289</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C74" s="19" t="s">
         <v>281</v>
@@ -18093,7 +18260,7 @@
         <v>291</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C75" s="19" t="s">
         <v>292</v>
@@ -18201,7 +18368,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B8" s="32" t="n">
         <f aca="false">COUNTIF(单一被试!$J$2:$J$46,"不达标")</f>
@@ -18257,7 +18424,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E13" s="30" t="s">
         <v>3</v>
@@ -18307,7 +18474,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B16" s="32" t="n">
         <f aca="false">COUNTIFS(单一被试!$J$2:$J$46,"不达标",单一被试!$K$2:$K$46,"无保留")</f>
@@ -18444,7 +18611,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B30" s="32" t="n">
         <f aca="false">COUNTIF(组间设计!$I$2:$I$10,"不达标")</f>
@@ -18758,7 +18925,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B8" s="32" t="n">
         <f aca="false">COUNTIF(母本单一被试!$K$2:$K$26,"不达标")</f>
@@ -18811,7 +18978,7 @@
         <v>18</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E13" s="30" t="s">
         <v>3</v>
@@ -18861,7 +19028,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B16" s="32" t="n">
         <f aca="false">COUNTIFS(母本单一被试!$K$2:$K$26,"不达标",母本单一被试!$L$2:$L$26,"无保留")</f>
@@ -18998,7 +19165,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B30" s="32" t="n">
         <f aca="false">COUNTIF(母本组间设计!$J$2:$J$4,"不达标")</f>
@@ -19160,7 +19327,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="31" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B49" s="32" t="n">
         <f aca="false">COUNTIF(母本单一被试!$K$2:$K$26,"不达标")+COUNTIF(单一被试!$J:$J,"不达标")</f>
@@ -19276,7 +19443,7 @@
     </row>
     <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>379</v>
@@ -19354,7 +19521,7 @@
     </row>
     <row r="4" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>391</v>
@@ -19432,7 +19599,7 @@
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>402</v>
@@ -19510,7 +19677,7 @@
     </row>
     <row r="8" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>410</v>
@@ -19549,7 +19716,7 @@
     </row>
     <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>379</v>
@@ -19588,7 +19755,7 @@
     </row>
     <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>417</v>
@@ -19627,7 +19794,7 @@
     </row>
     <row r="11" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>422</v>
@@ -19696,7 +19863,7 @@
         <v>18</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L12" s="19" t="str">
         <f aca="false">IF(J12=K12,"一致","不一致")</f>
@@ -19705,7 +19872,7 @@
     </row>
     <row r="13" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>434</v>
@@ -19744,19 +19911,19 @@
     </row>
     <row r="14" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>438</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>439</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>440</v>
@@ -19771,10 +19938,10 @@
         <v>441</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L14" s="19" t="str">
         <f aca="false">IF(J14=K14,"一致","不一致")</f>
@@ -19783,7 +19950,7 @@
     </row>
     <row r="15" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>442</v>
@@ -19810,10 +19977,10 @@
         <v>445</v>
       </c>
       <c r="J15" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L15" s="19" t="str">
         <f aca="false">IF(J15=K15,"一致","不一致")</f>
@@ -19822,7 +19989,7 @@
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>446</v>
@@ -19867,7 +20034,7 @@
         <v>452</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>453</v>
@@ -19888,7 +20055,7 @@
         <v>457</v>
       </c>
       <c r="J17" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K17" s="19" t="s">
         <v>18</v>
@@ -19900,7 +20067,7 @@
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>458</v>
@@ -19939,7 +20106,7 @@
     </row>
     <row r="19" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>397</v>
@@ -19978,7 +20145,7 @@
     </row>
     <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>466</v>
@@ -20017,7 +20184,7 @@
     </row>
     <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>470</v>
@@ -20056,19 +20223,19 @@
     </row>
     <row r="22" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>402</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>475</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F22" s="19" t="s">
         <v>476</v>
@@ -20083,10 +20250,10 @@
         <v>477</v>
       </c>
       <c r="J22" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K22" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L22" s="19" t="str">
         <f aca="false">IF(J22=K22,"一致","不一致")</f>
@@ -20095,7 +20262,7 @@
     </row>
     <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>402</v>
@@ -20134,19 +20301,19 @@
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>481</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>482</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>483</v>
@@ -20161,10 +20328,10 @@
         <v>484</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L24" s="19" t="str">
         <f aca="false">IF(J24=K24,"一致","不一致")</f>
@@ -20212,7 +20379,7 @@
     </row>
     <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>489</v>
@@ -20290,7 +20457,7 @@
     </row>
     <row r="28" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>498</v>
@@ -20329,19 +20496,19 @@
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>505</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>506</v>
       </c>
       <c r="E29" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F29" s="19" t="s">
         <v>507</v>
@@ -20356,10 +20523,10 @@
         <v>508</v>
       </c>
       <c r="J29" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K29" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L29" s="19" t="str">
         <f aca="false">IF(J29=K29,"一致","不一致")</f>
@@ -20407,7 +20574,7 @@
     </row>
     <row r="31" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>515</v>
@@ -20446,19 +20613,19 @@
     </row>
     <row r="32" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>402</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>519</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>520</v>
@@ -20473,10 +20640,10 @@
         <v>521</v>
       </c>
       <c r="J32" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K32" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L32" s="19" t="str">
         <f aca="false">IF(J32=K32,"一致","不一致")</f>
@@ -20485,7 +20652,7 @@
     </row>
     <row r="33" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>522</v>
@@ -20524,7 +20691,7 @@
     </row>
     <row r="34" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>529</v>
@@ -20602,7 +20769,7 @@
     </row>
     <row r="36" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>402</v>
@@ -20629,10 +20796,10 @@
         <v>540</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K36" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L36" s="19" t="str">
         <f aca="false">IF(J36=K36,"一致","不一致")</f>
@@ -20641,7 +20808,7 @@
     </row>
     <row r="37" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>541</v>
@@ -20719,19 +20886,19 @@
     </row>
     <row r="39" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B39" s="19" t="s">
         <v>551</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>552</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F39" s="19" t="s">
         <v>553</v>
@@ -20746,10 +20913,10 @@
         <v>554</v>
       </c>
       <c r="J39" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K39" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L39" s="19" t="str">
         <f aca="false">IF(J39=K39,"一致","不一致")</f>
@@ -20758,7 +20925,7 @@
     </row>
     <row r="40" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B40" s="19" t="s">
         <v>555</v>
@@ -20836,7 +21003,7 @@
     </row>
     <row r="42" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>397</v>
@@ -20875,19 +21042,19 @@
     </row>
     <row r="43" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>571</v>
       </c>
       <c r="C43" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>572</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F43" s="19" t="s">
         <v>573</v>
@@ -20902,10 +21069,10 @@
         <v>574</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K43" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L43" s="19" t="str">
         <f aca="false">IF(J43=K43,"一致","不一致")</f>
@@ -21095,7 +21262,7 @@
     </row>
     <row r="2" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>595</v>
@@ -21127,7 +21294,7 @@
     </row>
     <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>597</v>
@@ -21154,24 +21321,24 @@
         <v>26</v>
       </c>
       <c r="J3" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>602</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>603</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F4" s="19" t="s">
         <v>543</v>
@@ -21183,27 +21350,27 @@
         <v>20</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J4" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>604</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>605</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F5" s="19" t="s">
         <v>606</v>
@@ -21215,27 +21382,27 @@
         <v>607</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J5" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>608</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>609</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F6" s="19" t="s">
         <v>543</v>
@@ -21247,15 +21414,15 @@
         <v>20</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>610</v>
@@ -21319,7 +21486,7 @@
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>618</v>
@@ -21669,7 +21836,7 @@
     </row>
     <row r="7" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>649</v>
@@ -21711,7 +21878,7 @@
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>652</v>
@@ -21753,7 +21920,7 @@
     </row>
     <row r="9" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="37" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>657</v>
@@ -21879,7 +22046,7 @@
     </row>
     <row r="12" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>422</v>
@@ -21921,7 +22088,7 @@
     </row>
     <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>676</v>
@@ -21951,10 +22118,10 @@
         <v>630</v>
       </c>
       <c r="K13" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L13" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M13" s="19" t="str">
         <f aca="false">IF(K13=L13,"一致","不一致")</f>
@@ -21963,7 +22130,7 @@
     </row>
     <row r="14" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>682</v>
@@ -22005,7 +22172,7 @@
     </row>
     <row r="15" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="37" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>686</v>
@@ -22038,7 +22205,7 @@
         <v>26</v>
       </c>
       <c r="L15" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M15" s="19" t="str">
         <f aca="false">IF(K15=L15,"一致","不一致")</f>
@@ -22047,7 +22214,7 @@
     </row>
     <row r="16" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>692</v>
@@ -22089,7 +22256,7 @@
     </row>
     <row r="17" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>697</v>
@@ -22101,7 +22268,7 @@
         <v>698</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F17" s="19" t="s">
         <v>699</v>
@@ -22119,10 +22286,10 @@
         <v>630</v>
       </c>
       <c r="K17" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L17" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M17" s="19" t="str">
         <f aca="false">IF(K17=L17,"一致","不一致")</f>
@@ -22131,7 +22298,7 @@
     </row>
     <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>701</v>
@@ -22173,7 +22340,7 @@
     </row>
     <row r="19" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>707</v>
@@ -22215,7 +22382,7 @@
     </row>
     <row r="20" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>397</v>
@@ -22257,7 +22424,7 @@
     </row>
     <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>397</v>
@@ -22299,7 +22466,7 @@
     </row>
     <row r="22" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>718</v>
@@ -22341,7 +22508,7 @@
     </row>
     <row r="23" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>397</v>
@@ -22383,7 +22550,7 @@
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>727</v>
@@ -22425,7 +22592,7 @@
     </row>
     <row r="25" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>730</v>
@@ -22467,7 +22634,7 @@
     </row>
     <row r="26" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="37" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>734</v>
@@ -22479,7 +22646,7 @@
         <v>735</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>736</v>
@@ -22500,7 +22667,7 @@
         <v>18</v>
       </c>
       <c r="L26" s="19" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M26" s="19" t="str">
         <f aca="false">IF(K26=L26,"一致","不一致")</f>
@@ -22576,7 +22743,7 @@
     </row>
     <row r="2" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>738</v>
@@ -22611,7 +22778,7 @@
     </row>
     <row r="3" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>744</v>
@@ -22646,7 +22813,7 @@
     </row>
     <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>747</v>
